--- a/backend/order/src/test/resources/workbooks/DS-ORDER-3X/kd/Knock-Down_2026.xlsx
+++ b/backend/order/src/test/resources/workbooks/DS-ORDER-3X/kd/Knock-Down_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,115 +427,175 @@
           <t>Qty</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>837</v>
+        <v>416</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>433</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>808</v>
+        <v>812</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>953</v>
+        <v>504</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>366</v>
+        <v>389</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>436</v>
+        <v>578</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>900</v>
+        <v>269</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>775</v>
+        <v>601</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>879</v>
+        <v>802</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>960</v>
+        <v>417</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>659</v>
+        <v>151</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -545,157 +605,237 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>401</v>
+        <v>131</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>322</v>
+        <v>245</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52</v>
+        <v>811</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>562</v>
+        <v>982</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>163</v>
+        <v>112</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>524</v>
+        <v>530</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>236</v>
+        <v>814</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>61</v>
+        <v>830</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>759</v>
+        <v>638</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>466</v>
+        <v>710</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>599</v>
+        <v>63</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>102</v>
+        <v>408</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>452</v>
+        <v>15</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>815</v>
+        <v>853</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>161</v>
+        <v>492</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>354</v>
+        <v>455</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -705,127 +845,192 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>497</v>
+        <v>75</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>773</v>
+        <v>237</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>571</v>
+        <v>91</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>278</v>
+        <v>48</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>418</v>
+        <v>403</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>454</v>
+        <v>638</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>143</v>
+        <v>543</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>502</v>
+        <v>738</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>212</v>
+        <v>68</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>414</v>
+        <v>665</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>595</v>
+        <v>459</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>584</v>
+        <v>216</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>763</v>
+        <v>963</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -835,7 +1040,12 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>262</v>
+        <v>302</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -845,97 +1055,147 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>83</v>
+        <v>44</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>805</v>
+        <v>532</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>341</v>
+        <v>725</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>956</v>
+        <v>639</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>101</v>
+        <v>700</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>697</v>
+        <v>378</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>443</v>
+        <v>680</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>366</v>
+        <v>171</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>338</v>
+        <v>292</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>618</v>
+        <v>371</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -945,77 +1205,1032 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>34</v>
+        <v>414</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>183</v>
+        <v>610</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>641</v>
+        <v>540</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>648</v>
+        <v>764</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>461</v>
+        <v>80</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>956</v>
+        <v>572</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>214</v>
+        <v>753</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>946</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>366</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>996</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>241</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>996</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>475</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>25450-P7200</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>598</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>29673-2F900</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>277</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>29673-2R060</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>426</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>119</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>84</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>311</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>979</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>29673-2F910</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>832</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>989</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>907</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>842</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>266</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>463</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>25450-P7200</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>586</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>25451-P7200</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>798</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>785</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>994</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>25451-P7200</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>707</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>25451-P7200</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>928</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>892</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>29673-2F900</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>503</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>29673-2F910</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>274</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>29673-2F910</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>401</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>28415-08400</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>392</v>
+      <c r="B89" t="n">
+        <v>817</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>703</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>245</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>432</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>538</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>19</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>862</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>264</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>105</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>25450-P7200</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>699</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>850</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>87</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>963</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>29673-2R060</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>497</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>372</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>925</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>285</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>29673-2R060</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>979</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>709</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>520</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>214</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>763</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>903</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>221</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>217</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>866</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>374</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>29673-2R060</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>807</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>29673-2F910</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>132</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>29673-2F910</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>702</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>28415-08400</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>514</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>16</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>990</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
       </c>
     </row>
   </sheetData>
